--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -69,27 +69,6 @@
   </si>
   <si>
     <t>Student 3:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">F02. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cautarea filmelor care au un anumit regizor (sau parti din numele regizorului).</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">F02. Covered source code </t>
@@ -611,6 +590,27 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>F02.  actualizarea stocului unui ingredient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1370,180 +1370,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1555,9 +1381,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1568,72 +1391,249 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1655,44 +1655,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>33868</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>537828</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>93134</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="1151468"/>
-          <a:ext cx="4271628" cy="2853266"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>71717</xdr:colOff>
       <xdr:row>9</xdr:row>
@@ -1712,7 +1674,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1746,6 +1708,44 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>365761</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>36912</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="365761" y="929640"/>
+          <a:ext cx="4358640" cy="2399112"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1753,16 +1753,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1709058</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>97971</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>924772</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>114614</xdr:rowOff>
+      <xdr:colOff>543773</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>16642</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1779,8 +1779,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3939540" y="4785360"/>
-          <a:ext cx="6068272" cy="2248214"/>
+          <a:off x="6574972" y="3581400"/>
+          <a:ext cx="6062830" cy="2237328"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2090,12 +2090,12 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="9"/>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="29" t="s">
@@ -2143,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P7" s="17">
         <v>235</v>
@@ -2158,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P8" s="17">
         <v>235</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -2178,8 +2178,8 @@
       <c r="P9" s="17"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B10" s="90" t="s">
-        <v>77</v>
+      <c r="B10" s="32" t="s">
+        <v>76</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -2231,355 +2231,363 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="9"/>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="58"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="62"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="40"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="34"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="58"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="Q6" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="Q6" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="I8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
+      <c r="R8" s="73"/>
+      <c r="S8" s="73"/>
       <c r="T8" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B9" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
+      <c r="C9" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
       <c r="I9" s="28"/>
-      <c r="Q9" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
+      <c r="Q9" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" s="73"/>
+      <c r="S9" s="73"/>
       <c r="T9" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+        <v>22</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="66"/>
+      <c r="Q10" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="43"/>
-      <c r="Q10" s="37" t="s">
+      <c r="R10" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="S10" s="37"/>
+      <c r="S10" s="73"/>
       <c r="T10" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B11" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
+        <v>26</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="46"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="69"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
+        <v>27</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="46"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="69"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
+        <v>28</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="46"/>
-      <c r="Q13" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="69"/>
+      <c r="Q13" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
+        <v>27</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="46"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="69"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="44"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="46"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="69"/>
       <c r="Q15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="R15" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="R15" s="50" t="s">
+      <c r="S15" s="74"/>
+      <c r="T15" s="74"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I16" s="67"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="69"/>
+      <c r="Q16" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="S15" s="50"/>
-      <c r="T15" s="50"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="46"/>
-      <c r="Q16" s="25" t="s">
+      <c r="R16" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="S16" s="59"/>
+      <c r="T16" s="59"/>
+    </row>
+    <row r="17" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I17" s="67"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="69"/>
+      <c r="Q17" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="R16" s="35" t="s">
+      <c r="R17" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-    </row>
-    <row r="17" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I17" s="44"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="46"/>
-      <c r="Q17" s="25" t="s">
+      <c r="S17" s="59"/>
+      <c r="T17" s="59"/>
+    </row>
+    <row r="18" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I18" s="67"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="69"/>
+      <c r="Q18" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="R17" s="35" t="s">
+      <c r="R18" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-    </row>
-    <row r="18" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I18" s="44"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="46"/>
-      <c r="Q18" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="R18" s="35" t="s">
+      <c r="S18" s="59"/>
+      <c r="T18" s="59"/>
+    </row>
+    <row r="19" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I19" s="67"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="69"/>
+      <c r="Q19" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="R19" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-    </row>
-    <row r="19" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I19" s="44"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="46"/>
-      <c r="Q19" s="31" t="s">
+      <c r="S19" s="59"/>
+      <c r="T19" s="59"/>
+    </row>
+    <row r="20" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I20" s="67"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="69"/>
+      <c r="Q20" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="R19" s="35" t="s">
+      <c r="R20" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-    </row>
-    <row r="20" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I20" s="44"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="46"/>
-      <c r="Q20" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="R20" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
+      <c r="S20" s="59"/>
+      <c r="T20" s="59"/>
     </row>
     <row r="21" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I21" s="44"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="46"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="69"/>
       <c r="Q21" s="25"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="59"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="44"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="46"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="69"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="44"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="46"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="69"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="47"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="49"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="R21:T21"/>
@@ -2596,14 +2604,6 @@
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="R17:T17"/>
     <mergeCell ref="R19:T19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2639,597 +2639,603 @@
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B1" s="9"/>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="40"/>
+      <c r="B3" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="62"/>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B5" s="8"/>
     </row>
     <row r="6" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="79" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="D6" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="E6" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
+      <c r="V6" s="79"/>
+    </row>
+    <row r="7" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="54"/>
-    </row>
-    <row r="7" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="95" t="s">
+      <c r="F7" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="99" t="s">
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="102" t="s">
+      <c r="O7" s="88"/>
+      <c r="P7" s="88"/>
+      <c r="Q7" s="88"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="53" t="s">
+      <c r="T7" s="89"/>
+      <c r="U7" s="89"/>
+      <c r="V7" s="89"/>
+    </row>
+    <row r="8" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="79"/>
+      <c r="C8" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="90"/>
+      <c r="F8" s="87" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="87"/>
+      <c r="J8" s="87" t="s">
+        <v>106</v>
+      </c>
+      <c r="K8" s="87"/>
+      <c r="L8" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="M8" s="87"/>
+      <c r="N8" s="88" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="88" t="s">
+        <v>88</v>
+      </c>
+      <c r="S8" s="82">
+        <v>0</v>
+      </c>
+      <c r="T8" s="82">
+        <v>1</v>
+      </c>
+      <c r="U8" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="T7" s="53"/>
-      <c r="U7" s="53"/>
-      <c r="V7" s="53"/>
-    </row>
-    <row r="8" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="54"/>
-      <c r="C8" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="95"/>
-      <c r="F8" s="99" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="99"/>
-      <c r="J8" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="K8" s="99"/>
-      <c r="L8" s="99" t="s">
-        <v>111</v>
-      </c>
-      <c r="M8" s="99"/>
-      <c r="N8" s="102" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" s="102" t="s">
-        <v>34</v>
-      </c>
-      <c r="P8" s="103" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="103" t="s">
-        <v>88</v>
-      </c>
-      <c r="R8" s="102" t="s">
-        <v>89</v>
-      </c>
-      <c r="S8" s="107">
-        <v>0</v>
-      </c>
-      <c r="T8" s="107">
-        <v>1</v>
-      </c>
-      <c r="U8" s="107" t="s">
+      <c r="V8" s="75" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="79"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="V8" s="110" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="54"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="100" t="s">
+      <c r="G9" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="100" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="100" t="s">
+      <c r="H9" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="100" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="100" t="s">
+      <c r="J9" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="100" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" s="100" t="s">
+      <c r="L9" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="100" t="s">
-        <v>46</v>
-      </c>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="102"/>
-      <c r="S9" s="107"/>
-      <c r="T9" s="107"/>
-      <c r="U9" s="107"/>
-      <c r="V9" s="111"/>
+      <c r="N9" s="88"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="84"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="76"/>
     </row>
     <row r="10" spans="2:22" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="91" t="s">
-        <v>90</v>
+        <v>46</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>89</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="96" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="101" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="J10" s="101"/>
-      <c r="K10" s="101" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="101"/>
-      <c r="M10" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="N10" s="105"/>
-      <c r="O10" s="105"/>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="105" t="s">
-        <v>103</v>
-      </c>
-      <c r="R10" s="106"/>
-      <c r="S10" s="108"/>
-      <c r="T10" s="108"/>
-      <c r="U10" s="108" t="s">
-        <v>103</v>
-      </c>
-      <c r="V10" s="109"/>
+      <c r="I10" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" s="43"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="V10" s="45"/>
     </row>
     <row r="11" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" s="101"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="101"/>
-      <c r="M11" s="101"/>
-      <c r="N11" s="105" t="s">
-        <v>103</v>
-      </c>
-      <c r="O11" s="105"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="106"/>
-      <c r="S11" s="108"/>
-      <c r="T11" s="108"/>
-      <c r="U11" s="108"/>
-      <c r="V11" s="109"/>
+        <v>96</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="45"/>
     </row>
     <row r="12" spans="2:22" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="92" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="93" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" s="101"/>
-      <c r="I12" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="101"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="N12" s="105"/>
-      <c r="O12" s="105" t="s">
-        <v>103</v>
-      </c>
-      <c r="P12" s="105"/>
-      <c r="Q12" s="105"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="108" t="s">
-        <v>103</v>
-      </c>
-      <c r="T12" s="108"/>
-      <c r="U12" s="108"/>
-      <c r="V12" s="109"/>
+        <v>90</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="45"/>
     </row>
     <row r="13" spans="2:22" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="96" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101" t="s">
+      <c r="H13" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="101" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="101"/>
-      <c r="J13" s="101" t="s">
+      <c r="I13" s="41"/>
+      <c r="J13" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="K13" s="101" t="s">
-        <v>109</v>
-      </c>
-      <c r="L13" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="M13" s="101"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="105"/>
-      <c r="R13" s="106" t="s">
-        <v>103</v>
-      </c>
-      <c r="S13" s="108"/>
-      <c r="T13" s="108"/>
-      <c r="U13" s="108"/>
-      <c r="V13" s="109" t="s">
-        <v>103</v>
+      <c r="L13" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="M13" s="41"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="45" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="2:22" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B14" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="D14" t="s">
         <v>113</v>
       </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="98" t="s">
+      <c r="E14" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101" t="s">
+      <c r="H14" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="101" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="101"/>
-      <c r="J14" s="101" t="s">
-        <v>109</v>
-      </c>
-      <c r="K14" s="101"/>
-      <c r="L14" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="M14" s="101"/>
-      <c r="N14" s="105"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="105" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q14" s="105"/>
-      <c r="R14" s="106"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="108"/>
-      <c r="U14" s="108"/>
-      <c r="V14" s="109" t="s">
-        <v>103</v>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="M14" s="41"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="45" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="101"/>
-      <c r="M15" s="101"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="106"/>
-      <c r="R15" s="106"/>
-      <c r="S15" s="108"/>
-      <c r="T15" s="108"/>
-      <c r="U15" s="108"/>
-      <c r="V15" s="109"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="45"/>
     </row>
     <row r="16" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="12"/>
     </row>
     <row r="17" spans="13:21" x14ac:dyDescent="0.3">
-      <c r="M17" s="112"/>
-      <c r="N17" s="112"/>
-      <c r="O17" s="112"/>
-      <c r="P17" s="112"/>
-      <c r="Q17" s="112"/>
-      <c r="R17" s="112"/>
-      <c r="S17" s="112"/>
-      <c r="T17" s="112"/>
-      <c r="U17" s="112"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
     </row>
     <row r="18" spans="13:21" x14ac:dyDescent="0.3">
-      <c r="M18" s="112"/>
-      <c r="N18" s="112"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
     </row>
     <row r="19" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M19" s="112"/>
-      <c r="N19" s="113"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="113"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
     </row>
     <row r="20" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M20" s="112"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="112"/>
-      <c r="S20" s="112"/>
-      <c r="T20" s="112"/>
-      <c r="U20" s="112"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="78"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="46"/>
+      <c r="U20" s="46"/>
     </row>
     <row r="21" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M21" s="112"/>
-      <c r="N21" s="114"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="46"/>
+      <c r="U21" s="46"/>
     </row>
     <row r="22" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M22" s="112"/>
-      <c r="N22" s="114"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="112"/>
-      <c r="R22" s="112"/>
-      <c r="S22" s="112"/>
-      <c r="T22" s="112"/>
-      <c r="U22" s="112"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
     </row>
     <row r="23" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M23" s="112"/>
-      <c r="N23" s="114"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="115"/>
-      <c r="Q23" s="112"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="112"/>
-      <c r="T23" s="112"/>
-      <c r="U23" s="112"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="46"/>
+      <c r="U23" s="46"/>
     </row>
     <row r="24" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M24" s="112"/>
-      <c r="N24" s="114"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="115"/>
-      <c r="Q24" s="112"/>
-      <c r="R24" s="112"/>
-      <c r="S24" s="112"/>
-      <c r="T24" s="112"/>
-      <c r="U24" s="112"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
     </row>
     <row r="25" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M25" s="112"/>
-      <c r="N25" s="114"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="112"/>
-      <c r="R25" s="116"/>
-      <c r="S25" s="116"/>
-      <c r="T25" s="116"/>
-      <c r="U25" s="116"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="47"/>
+      <c r="O25" s="47"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="77"/>
+      <c r="S25" s="77"/>
+      <c r="T25" s="77"/>
+      <c r="U25" s="77"/>
     </row>
     <row r="26" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M26" s="112"/>
-      <c r="N26" s="114"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="115"/>
-      <c r="Q26" s="112"/>
-      <c r="R26" s="116"/>
-      <c r="S26" s="116"/>
-      <c r="T26" s="116"/>
-      <c r="U26" s="116"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="77"/>
+      <c r="S26" s="77"/>
+      <c r="T26" s="77"/>
+      <c r="U26" s="77"/>
     </row>
     <row r="27" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M27" s="112"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
-      <c r="Q27" s="112"/>
-      <c r="R27" s="114"/>
-      <c r="S27" s="114"/>
-      <c r="T27" s="114"/>
-      <c r="U27" s="115"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="48"/>
     </row>
     <row r="28" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M28" s="112"/>
-      <c r="N28" s="112"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="112"/>
-      <c r="R28" s="114"/>
-      <c r="S28" s="114"/>
-      <c r="T28" s="114"/>
-      <c r="U28" s="115"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="47"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="48"/>
     </row>
     <row r="29" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="112"/>
-      <c r="R29" s="114"/>
-      <c r="S29" s="114"/>
-      <c r="T29" s="114"/>
-      <c r="U29" s="115"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="48"/>
     </row>
     <row r="30" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="112"/>
-      <c r="R30" s="114"/>
-      <c r="S30" s="114"/>
-      <c r="T30" s="114"/>
-      <c r="U30" s="115"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="47"/>
+      <c r="S30" s="47"/>
+      <c r="T30" s="47"/>
+      <c r="U30" s="48"/>
     </row>
     <row r="31" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="114"/>
-      <c r="S31" s="114"/>
-      <c r="T31" s="114"/>
-      <c r="U31" s="115"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="47"/>
+      <c r="S31" s="47"/>
+      <c r="T31" s="47"/>
+      <c r="U31" s="48"/>
     </row>
     <row r="32" spans="13:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="M32" s="112"/>
-      <c r="N32" s="112"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="112"/>
-      <c r="Q32" s="112"/>
-      <c r="R32" s="114"/>
-      <c r="S32" s="114"/>
-      <c r="T32" s="114"/>
-      <c r="U32" s="115"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="46"/>
+      <c r="Q32" s="46"/>
+      <c r="R32" s="47"/>
+      <c r="S32" s="47"/>
+      <c r="T32" s="47"/>
+      <c r="U32" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="U25:U26"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="N7:R7"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="P19:P20"/>
@@ -3246,17 +3252,11 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="R8:R9"/>
     <mergeCell ref="P8:P9"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="N7:R7"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="U25:U26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3285,185 +3285,185 @@
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="9"/>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="93" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="80" t="s">
+      <c r="C4" s="101" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="D4" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="88" t="s">
+      <c r="E4" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="82" t="s">
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="82" t="s">
+      <c r="I4" s="97"/>
+    </row>
+    <row r="5" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="95"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="83"/>
-    </row>
-    <row r="5" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="81"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="13">
         <v>9</v>
       </c>
-      <c r="C6" s="84" t="s">
-        <v>57</v>
+      <c r="C6" s="98" t="s">
+        <v>56</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="117" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="121" t="s">
-        <v>129</v>
+        <v>46</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>128</v>
       </c>
       <c r="H6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="15" x14ac:dyDescent="0.35">
       <c r="B7" s="13">
         <v>10</v>
       </c>
-      <c r="C7" s="84"/>
+      <c r="C7" s="98"/>
       <c r="D7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="118" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="90" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="I7" s="94" t="s">
-        <v>133</v>
+        <v>57</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="13">
         <v>11</v>
       </c>
-      <c r="C8" s="84"/>
+      <c r="C8" s="98"/>
       <c r="D8" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="118" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="90" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="122" t="s">
-        <v>131</v>
+        <v>90</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="54" t="s">
+        <v>130</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="15" x14ac:dyDescent="0.35">
       <c r="B9" s="13">
         <v>12</v>
       </c>
-      <c r="C9" s="84"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="118" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="90" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="90" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="I9" s="94" t="s">
-        <v>133</v>
+      <c r="I9" s="36" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="85"/>
+      <c r="C10" s="99"/>
       <c r="D10" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="119" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="120" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="G10" s="90" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="I10" s="94" t="s">
-        <v>133</v>
+      <c r="H10" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -3478,71 +3478,71 @@
     </row>
     <row r="12" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="2:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="2:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="71" t="s">
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="65" t="s">
+      <c r="G13" s="106"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="66"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="77" t="s">
+      <c r="K13" s="117"/>
+    </row>
+    <row r="14" spans="2:11" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="78"/>
-    </row>
-    <row r="14" spans="2:11" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="57" t="s">
+      <c r="C14" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="D14" s="119" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="E14" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="61" t="s">
+      <c r="F14" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="63" t="s">
+      <c r="G14" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="H14" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="69" t="s">
+      <c r="I14" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="74" t="s">
+      <c r="J14" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="J14" s="76" t="s">
+      <c r="K14" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="K14" s="68" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="58"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="63"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="115"/>
+      <c r="K15" s="108"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="17">
@@ -3554,23 +3554,23 @@
       <c r="D16" s="15">
         <v>0</v>
       </c>
-      <c r="E16" s="123">
+      <c r="E16" s="55">
         <v>1</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H16" s="18">
         <v>0</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K16" s="20">
         <f>C16</f>
@@ -3579,6 +3579,18 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J13:K13"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:I3"/>
@@ -3589,18 +3601,6 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3608,9 +3608,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3752,26 +3755,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3795,9 +3787,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>